--- a/data/trans_bre/P15-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P15-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 3,29</t>
+          <t>-5,37; 2,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 2,58</t>
+          <t>-8,85; 2,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 8,72</t>
+          <t>-0,48; 9,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 5,08</t>
+          <t>-3,98; 5,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-60,47; 67,54</t>
+          <t>-61,09; 55,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-53,54; 26,15</t>
+          <t>-54,95; 26,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 198,51</t>
+          <t>-7,11; 197,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 83,13</t>
+          <t>-32,66; 87,02</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 2,05</t>
+          <t>-3,07; 2,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 2,4</t>
+          <t>-3,5; 2,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 1,5</t>
+          <t>-3,12; 1,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 4,65</t>
+          <t>-1,28; 4,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,2; 76,59</t>
+          <t>-54,85; 80,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,31; 50,23</t>
+          <t>-45,19; 53,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-63,34; 60,32</t>
+          <t>-61,08; 60,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,44; 149,77</t>
+          <t>-22,44; 154,84</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,81; -1,39</t>
+          <t>-9,66; -1,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 1,71</t>
+          <t>-9,44; 0,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,81; -0,03</t>
+          <t>-7,06; 0,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 4,1</t>
+          <t>-2,71; 4,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-75,25; -11,36</t>
+          <t>-77,61; -13,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,12; 14,7</t>
+          <t>-50,39; 7,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-74,87; 5,61</t>
+          <t>-73,44; 9,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-29,8; 82,89</t>
+          <t>-31,76; 93,15</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,7; -1,73</t>
+          <t>-9,53; -1,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,65; -0,61</t>
+          <t>-8,25; -0,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 3,5</t>
+          <t>-5,62; 3,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 0,05</t>
+          <t>-8,7; 0,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,67; -16,83</t>
+          <t>-70,83; -13,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,44; -7,26</t>
+          <t>-71,95; -5,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,39; 41,2</t>
+          <t>-45,15; 43,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-79,35; 6,34</t>
+          <t>-77,86; 10,94</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 1,72</t>
+          <t>-9,05; 2,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 8,34</t>
+          <t>-2,39; 7,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 0,73</t>
+          <t>-6,25; 0,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,7; -1,49</t>
+          <t>-7,36; -1,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-72,18; 34,84</t>
+          <t>-70,76; 40,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 219,0</t>
+          <t>-28,93; 188,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-90,72; 49,89</t>
+          <t>-89,98; 47,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -25,89</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 4,76</t>
+          <t>-4,25; 4,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 7,14</t>
+          <t>-4,14; 7,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 8,77</t>
+          <t>-2,61; 8,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 5,05</t>
+          <t>-3,71; 5,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,13; 94,83</t>
+          <t>-44,74; 94,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 91,82</t>
+          <t>-29,52; 88,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,51; 112,84</t>
+          <t>-20,32; 105,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,47; 67,31</t>
+          <t>-30,32; 90,32</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,45; -1,0</t>
+          <t>-6,26; -0,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 2,0</t>
+          <t>-4,46; 1,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 2,25</t>
+          <t>-2,44; 2,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 2,2</t>
+          <t>-5,36; 2,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-68,98; -14,9</t>
+          <t>-70,58; -15,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-37,95; 25,22</t>
+          <t>-39,38; 22,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-43,82; 84,24</t>
+          <t>-47,58; 72,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-60,09; 35,94</t>
+          <t>-64,57; 36,17</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,07</t>
+          <t>-2,93; 1,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,93</t>
+          <t>-1,58; 2,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,7</t>
+          <t>-3,08; 0,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,59</t>
+          <t>-0,74; 3,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,47; 39,73</t>
+          <t>-37,22; 38,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,96; 87,27</t>
+          <t>-41,93; 92,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-57,58; 19,9</t>
+          <t>-57,36; 24,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,27; 249,2</t>
+          <t>-22,76; 247,73</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,46; -1,03</t>
+          <t>-3,42; -1,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,03</t>
+          <t>-2,26; 0,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,69</t>
+          <t>-1,67; 0,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,57</t>
+          <t>-1,37; 1,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-42,52; -14,97</t>
+          <t>-42,74; -15,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-27,97; 0,51</t>
+          <t>-25,06; 2,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 13,38</t>
+          <t>-26,6; 11,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 30,97</t>
+          <t>-21,49; 31,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P15-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P15-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 2,71</t>
+          <t>-5,08; 3,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 2,33</t>
+          <t>-8,42; 2,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 9,01</t>
+          <t>-0,99; 8,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 5,29</t>
+          <t>-3,09; 4,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-61,09; 55,02</t>
+          <t>-59,77; 74,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,95; 26,07</t>
+          <t>-54,58; 19,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 197,1</t>
+          <t>-13,89; 198,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-32,66; 87,02</t>
+          <t>-28,71; 77,27</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 2,16</t>
+          <t>-3,0; 2,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 2,5</t>
+          <t>-3,18; 2,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,52</t>
+          <t>-3,2; 1,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 4,63</t>
+          <t>-1,59; 4,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,85; 80,87</t>
+          <t>-53,38; 85,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,19; 53,78</t>
+          <t>-41,84; 63,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,08; 60,22</t>
+          <t>-63,68; 54,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 154,84</t>
+          <t>-25,72; 144,64</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,66; -1,37</t>
+          <t>-9,8; -1,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 0,99</t>
+          <t>-9,96; 0,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 0,34</t>
+          <t>-7,39; 0,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 4,57</t>
+          <t>-3,16; 3,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-77,61; -13,62</t>
+          <t>-76,98; -14,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,39; 7,84</t>
+          <t>-50,46; 6,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-73,44; 9,7</t>
+          <t>-74,84; 12,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-31,76; 93,15</t>
+          <t>-34,38; 72,51</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,77</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-49,62%</t>
+          <t>-38,94%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,53; -1,3</t>
+          <t>-10,19; -1,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,25; -0,52</t>
+          <t>-8,61; -0,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 3,53</t>
+          <t>-5,46; 3,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 0,32</t>
+          <t>-7,87; 1,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,83; -13,99</t>
+          <t>-71,61; -13,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,95; -5,49</t>
+          <t>-74,56; -9,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,15; 43,27</t>
+          <t>-43,4; 48,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-77,86; 10,94</t>
+          <t>-72,88; 40,08</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,72</t>
+          <t>-3,41</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-93,5%</t>
+          <t>-93,65%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 2,23</t>
+          <t>-8,97; 2,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 7,85</t>
+          <t>-1,88; 8,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 0,57</t>
+          <t>-6,41; 0,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,36; -1,57</t>
+          <t>-7,34; -1,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,76; 40,84</t>
+          <t>-71,66; 33,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,93; 188,14</t>
+          <t>-24,46; 206,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-89,98; 47,07</t>
+          <t>-91,74; 26,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -25,89</t>
+          <t>-100,0; -14,0</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 4,79</t>
+          <t>-4,37; 5,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 7,3</t>
+          <t>-3,61; 7,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 8,36</t>
+          <t>-2,77; 8,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 5,9</t>
+          <t>-2,86; 5,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,74; 94,69</t>
+          <t>-44,68; 113,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,52; 88,34</t>
+          <t>-27,2; 97,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 105,94</t>
+          <t>-22,43; 105,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,32; 90,32</t>
+          <t>-25,21; 73,02</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,06</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-15,21%</t>
+          <t>-2,39%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,26; -0,94</t>
+          <t>-6,3; -0,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 1,78</t>
+          <t>-4,51; 1,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,16</t>
+          <t>-2,38; 2,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 2,06</t>
+          <t>-3,17; 2,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-70,58; -15,22</t>
+          <t>-69,16; -15,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-39,38; 22,42</t>
+          <t>-39,51; 22,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-47,58; 72,38</t>
+          <t>-46,77; 76,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-64,57; 36,17</t>
+          <t>-32,41; 44,66</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,96</t>
+          <t>-2,9; 2,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,04</t>
+          <t>-1,72; 1,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,82</t>
+          <t>-3,03; 0,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,49</t>
+          <t>-1,81; 2,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,22; 38,34</t>
+          <t>-37,51; 40,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 92,58</t>
+          <t>-45,25; 84,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-57,36; 24,42</t>
+          <t>-56,02; 23,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 247,73</t>
+          <t>-37,05; 95,02</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>-0,65%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,42; -1,04</t>
+          <t>-3,4; -1,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,18</t>
+          <t>-2,56; 0,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,6</t>
+          <t>-1,53; 0,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,55</t>
+          <t>-1,14; 1,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-42,74; -15,09</t>
+          <t>-42,0; -15,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 2,46</t>
+          <t>-28,57; 1,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-26,6; 11,55</t>
+          <t>-24,2; 10,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 31,86</t>
+          <t>-16,53; 19,23</t>
         </is>
       </c>
     </row>
